--- a/public/templates/无损检测题目导入模板.xlsx
+++ b/public/templates/无损检测题目导入模板.xlsx
@@ -1212,17 +1212,17 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:J1"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2 I3:I1048576">
       <formula1>"单选题,判断题,多选题"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2 J3:J1048576">
       <formula1>"无损检测人员"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 C2:H2" numberStoredAsText="1"/>
+    <ignoredError sqref="C2:H2 A1:H1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>